--- a/final_v0/final_pipeline_v2/artifacts/studies/static_line_b_staged_v2/20260820_144230_stage-ablation-01-static-peak-detectors-v1/result_backup/tables/report_tables.xlsx
+++ b/final_v0/final_pipeline_v2/artifacts/studies/static_line_b_staged_v2/20260820_144230_stage-ablation-01-static-peak-detectors-v1/result_backup/tables/report_tables.xlsx
@@ -2,9 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheets>
-    <sheet name="static_peak_detector_summary" sheetId="1" r:id="rId1"/>
-    <sheet name="table_figure_pairs" sheetId="2" r:id="rId2"/>
-    <sheet name="test_components" sheetId="3" r:id="rId3"/>
+    <sheet name="reporter_profiles" sheetId="1" r:id="rId1"/>
+    <sheet name="result_comparison" sheetId="2" r:id="rId2"/>
+    <sheet name="result_conclusions" sheetId="3" r:id="rId3"/>
+    <sheet name="static_peak_detector_summary" sheetId="4" r:id="rId4"/>
+    <sheet name="table_figure_pairs" sheetId="5" r:id="rId5"/>
+    <sheet name="test_components" sheetId="6" r:id="rId6"/>
   </sheets>
 </workbook>
 </file>
@@ -12,20 +15,37 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <fonts count="1">
-    <font/>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
   </fonts>
-  <fills count="1">
-    <fill/>
+  <fills count="2">
+    <fill>
+      <patternFill patternType="none"/>
+    </fill>
+    <fill>
+      <patternFill patternType="gray125"/>
+    </fill>
   </fills>
   <borders count="1">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  </cellStyles>
 </styleSheet>
 </file>
 
@@ -35,260 +55,201 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t xml:space="preserve">algorithm_or_reducer</t>
+          <t xml:space="preserve">profile_id</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t xml:space="preserve">activity_group</t>
+          <t xml:space="preserve">title</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t xml:space="preserve">channel</t>
+          <t xml:space="preserve">algorithm_summary</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t xml:space="preserve">participant_count</t>
+          <t xml:space="preserve">statistical_methods</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t xml:space="preserve">segment_count</t>
+          <t xml:space="preserve">required_tables</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t xml:space="preserve">participant_macro_f1_mean_sd</t>
+          <t xml:space="preserve">required_figures</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t xml:space="preserve">participant_macro_sensitivity_mean_sd</t>
+          <t xml:space="preserve">literature</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t xml:space="preserve">participant_macro_positive_predictive_value_mean_sd</t>
+          <t xml:space="preserve">limitations</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t xml:space="preserve">participant_macro_ibi_ppi_rmse_ms_mean_sd</t>
+          <t xml:space="preserve">profile_kind</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t xml:space="preserve">total_runtime_s</t>
+          <t xml:space="preserve">participating_components</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">module_references</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">presentation_only</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">changes_training_or_predictions</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">aboy_project_v1</t>
+          <t xml:space="preserve">audit_provenance_v1</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">static</t>
+          <t xml:space="preserve">Configuration and provenance audit</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">IR</t>
+          <t xml:space="preserve">Persisted resolved configuration, input data, seeds, splits, status and artifact inventory are projected without changing the experiment.</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22</t>
+          <t xml:space="preserve">[]</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198</t>
+          <t xml:space="preserve">["test_components", "reproducibility_summary"]</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t xml:space="preserve">96.8 ± 7.9</t>
+          <t xml:space="preserve">[]</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t xml:space="preserve">96.6 ± 10.9</t>
+          <t xml:space="preserve">[]</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t xml:space="preserve">98.0 ± 5.4</t>
+          <t xml:space="preserve">[]</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t xml:space="preserve">24.8 ± 20.5</t>
+          <t xml:space="preserve">endpoint_or_module</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.9318563170963898</t>
+          <t xml:space="preserve">["dataset_adapter:ptt_ppg_1_1_0_local", "peak_detector:aboy_project_v1", "peak_detector:msptdfast_v2_3_python_port", "peak_validation:paper_toolbox_style_lag_search_in_consecutive_time_windows"]</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">["Charlton et al. (2025), MSPTDfast (v.2), DOI:10.1088/1361-6579/adb89e", "Historical project adaptation; algorithm family: Aboy et al. (2005), DOI:10.1109/TBME.2005.855725", "Project component-role audit binding: dataset_adapter; no separate external literature source claimed", "Project component-role audit binding: peak_validation; no separate external literature source claimed"]</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">True</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">False</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">aboy_project_v1</t>
+          <t xml:space="preserve">beat_detector_legacy_persisted_v1</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">static</t>
+          <t xml:space="preserve">Historical PPG beat-detector report</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">RED</t>
+          <t xml:space="preserve">Historical detector outputs are regenerated only with the lag window, beat tolerance, aggregation and metrics persisted in that run's resolved_plan.yaml; the later 300 s/±150 ms contract is not back-applied.</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22</t>
+          <t xml:space="preserve">["Exact historical validation settings are displayed from resolved_plan.yaml.", "Historical summaries remain historical evidence and are not relabeled as current-contract results."]</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198</t>
+          <t xml:space="preserve">["static_peak_detector_summary"]</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t xml:space="preserve">95.6 ± 7.8</t>
+          <t xml:space="preserve">["static_peak_detector_f1", "static_peak_detector_sensitivity", "static_peak_detector_ppv", "static_peak_detector_interval_rmse", "static_peak_detector_runtime"]</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t xml:space="preserve">96.4 ± 10.2</t>
+          <t xml:space="preserve">["Current comparison paper retained for context only: Charlton et al. (2025), DOI:10.1088/1361-6579/adb89e"]</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t xml:space="preserve">96.0 ± 7.7</t>
+          <t xml:space="preserve">["Do not pool this profile with current-contract 300 s/±150 ms recording-level results."]</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t xml:space="preserve">35.1 ± 37.6</t>
+          <t xml:space="preserve">endpoint_or_module</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.9547193309408613</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">msptdfast_v2_3_python_port</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">static</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">IR</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">22</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">198</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">97.8 ± 0.5</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">98.6 ± 0.5</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">97.1 ± 0.5</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">16.8 ± 14.6</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.39543810294708237</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">msptdfast_v2_3_python_port</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">static</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">RED</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">22</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">198</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">96.6 ± 3.2</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">97.3 ± 3.8</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">96.0 ± 2.7</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">25.5 ± 27.1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.393930005870061</t>
+          <t xml:space="preserve">["peak_detector:aboy_project_v1", "peak_detector:msptdfast_v2_3_python_port", "peak_validation:paper_toolbox_style_lag_search_in_consecutive_time_windows"]</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">["Charlton et al. (2025), MSPTDfast (v.2), DOI:10.1088/1361-6579/adb89e", "Historical project adaptation; algorithm family: Aboy et al. (2005), DOI:10.1109/TBME.2005.855725", "Project component-role audit binding: peak_validation; no separate external literature source claimed"]</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">True</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">False</t>
         </is>
       </c>
     </row>
@@ -302,162 +263,235 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t xml:space="preserve">table</t>
+          <t xml:space="preserve">evidence_type</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t xml:space="preserve">table_status</t>
+          <t xml:space="preserve">activity_group</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t xml:space="preserve">figure</t>
+          <t xml:space="preserve">algorithm_or_reducer</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t xml:space="preserve">figure_status</t>
+          <t xml:space="preserve">channel</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t xml:space="preserve">figure_path</t>
+          <t xml:space="preserve">participant_count</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">participant_macro_f1</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">participant_macro_ibi_ppi_rmse_ms</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">segment_count</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">total_runtime_s</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">static_peak_detector_summary</t>
+          <t xml:space="preserve">peak_detector</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">available</t>
+          <t xml:space="preserve">static</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">static_peak_detector_f1</t>
+          <t xml:space="preserve">aboy_project_v1</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">generated</t>
+          <t xml:space="preserve">IR</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">figures/static_peak_detector_f1.png</t>
+          <t xml:space="preserve">22</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0.9678856748506576</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24.848360018965128</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">198</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1.9318563170963898</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">static_peak_detector_summary</t>
+          <t xml:space="preserve">peak_detector</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">available</t>
+          <t xml:space="preserve">static</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">static_peak_detector_sensitivity</t>
+          <t xml:space="preserve">aboy_project_v1</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">generated</t>
+          <t xml:space="preserve">RED</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">figures/static_peak_detector_sensitivity.png</t>
+          <t xml:space="preserve">22</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0.9559098959265971</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">35.0957617208711</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">198</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1.9547193309408613</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">static_peak_detector_summary</t>
+          <t xml:space="preserve">peak_detector</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">available</t>
+          <t xml:space="preserve">static</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">static_peak_detector_ppv</t>
+          <t xml:space="preserve">msptdfast_v2_3_python_port</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">generated</t>
+          <t xml:space="preserve">IR</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">figures/static_peak_detector_ppv.png</t>
+          <t xml:space="preserve">22</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0.9784641356233297</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16.757007954683708</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">198</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0.39543810294708237</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">static_peak_detector_summary</t>
+          <t xml:space="preserve">peak_detector</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">available</t>
+          <t xml:space="preserve">static</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">static_peak_detector_interval_rmse</t>
+          <t xml:space="preserve">msptdfast_v2_3_python_port</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">generated</t>
+          <t xml:space="preserve">RED</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">figures/static_peak_detector_interval_rmse.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">static_peak_detector_summary</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">available</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">static_peak_detector_runtime</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">generated</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">figures/static_peak_detector_runtime.png</t>
+          <t xml:space="preserve">22</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0.9661126884492686</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">25.48290823570446</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">198</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0.393930005870061</t>
         </is>
       </c>
     </row>
@@ -471,157 +505,826 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t xml:space="preserve">participating_cases</t>
+          <t xml:space="preserve">angle</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t xml:space="preserve">component_role</t>
+          <t xml:space="preserve">leading_or_selected_case</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t xml:space="preserve">module_id</t>
+          <t xml:space="preserve">finding</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t xml:space="preserve">execution_state</t>
+          <t xml:space="preserve">confidence</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t xml:space="preserve">input_data</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">fixed_parameters</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">algorithm_kernel_description</t>
+          <t xml:space="preserve">selection_effect</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">all</t>
+          <t xml:space="preserve">beat_detection_accuracy</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">dataset_adapter</t>
+          <t xml:space="preserve">msptdfast_v2_3_python_port</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ptt_ppg_1_1_0_local</t>
+          <t xml:space="preserve">Highest historical participant-macro F1 under persisted legacy validation: 97.8% on channel IR.</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">enabled</t>
+          <t xml:space="preserve">historical_contract_not_poolable_with_v3</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"activities":["sit","walk","run"],"channels":{"IR":"pleth_2","RED":"pleth_1"},"dataset_id":"ptt_ppg_1_1_0_local","dataset_root":"physionet.org/files/pulse-transit-time-ppg/1.1.0","ecg_peak_annotation_column":"peaks","participants":22,"pipeline_fs_hz":400.0,"records":66,"source_fs_hz":500.0}</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{"activities":["sit","walk","run"],"dataset_id":"ptt_ppg_1_1_0_local","distal_channels":{"IR":"pleth_2","RED":"pleth_1"},"ecg_peak_annotation_column":"peaks","participant_count":22,"record_count":66,"root":"physionet.org/files/pulse-transit-time-ppg/1.1.0","selected_activity":"sit","selected_record_count":22}</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">manual_default_review_only</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">PTT sit static peak ablation</t>
+          <t xml:space="preserve">statistical_comparison</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">peak_detector</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t xml:space="preserve">No current-contract recording-level corrected P-value family is available.</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">not_available</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">none_automatic</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">activity_group</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">algorithm_or_reducer</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">channel</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">participant_count</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">participant_macro_f1</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">participant_macro_ibi_ppi_rmse_ms</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">segment_count</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">total_runtime_s</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">static</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
           <t xml:space="preserve">aboy_project_v1</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IR</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0.9678856748506576</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24.848360018965128</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">198</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1.9318563170963898</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">static</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">aboy_project_v1</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RED</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">executed</t>
+          <t xml:space="preserve">22</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"activities":["sit","walk","run"],"channels":["RED","IR"],"dataset_id":"ptt_ppg_1_1_0_local","dataset_root":"physionet.org/files/pulse-transit-time-ppg/1.1.0","ecg_peak_annotation_column":"peaks","input_view":null,"participants":22,"pipeline_fs_hz":400.0,"records":66,"scoring_windows_s":60.0,"selected_activity":"sit","source_fs_hz":500.0}</t>
+          <t xml:space="preserve">0.9559098959265971</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"adaptive_bandpass_hz":"0.5 to min(8,max(1.5,3*(1+HRI)))","algorithm_id":"aboy_project_v1","bandpass_order":2,"block_s":10.0,"implementation":"ppg_frailty.peaks.aboy_project","initial_hri":0.0,"input_preprocessing":"shared repaired PPG then shared 0.2-8 Hz analysis filter","mad_limit":4.0,"mad_scale":1.4826,"prominence_fraction":0.25,"pulse_rate_bpm":[35.0,210.0],"role":"current_project_reference"}</t>
+          <t xml:space="preserve">35.0957617208711</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">198</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1.9547193309408613</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">PTT sit static peak ablation</t>
+          <t xml:space="preserve">static</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">peak_detector</t>
+          <t xml:space="preserve">msptdfast_v2_3_python_port</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">msptdfast_v2_3_python_port</t>
+          <t xml:space="preserve">IR</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">executed</t>
+          <t xml:space="preserve">22</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"activities":["sit","walk","run"],"channels":["RED","IR"],"dataset_id":"ptt_ppg_1_1_0_local","dataset_root":"physionet.org/files/pulse-transit-time-ppg/1.1.0","ecg_peak_annotation_column":"peaks","input_view":null,"participants":22,"pipeline_fs_hz":400.0,"records":66,"scoring_windows_s":60.0,"selected_activity":"sit","source_fs_hz":500.0}</t>
+          <t xml:space="preserve">0.9784641356233297</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"algorithm_id":"msptdfast_v2_3_python_port","implementation":"ppg_frailty.quality.stage5_pre.detect_msptdfast_v2","parameters":{"minimum_heart_rate_bpm":30.0,"overlap_fraction":0.2,"target_downsample_hz":20.0,"window_s":6.0},"parity_status":"equation_level_port_not_bitwise_matlab_validated","role":"paper_method_comparator"}</t>
+          <t xml:space="preserve">16.757007954683708</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">198</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0.39543810294708237</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t xml:space="preserve">static</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">msptdfast_v2_3_python_port</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RED</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0.9661126884492686</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">25.48290823570446</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">198</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0.393930005870061</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">table</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">table_status</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">figure</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">figure_status</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">figure_path</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">static_peak_detector_summary</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">available</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">static_peak_detector_f1</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">generated</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">figures/static_peak_detector_f1.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">static_peak_detector_recording_metrics</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">not_registered</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">static_peak_detector_f1</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">generated</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">figures/static_peak_detector_f1.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">static_peak_detector_summary</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">available</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">static_peak_detector_sensitivity</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">generated</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">figures/static_peak_detector_sensitivity.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">static_peak_detector_recording_metrics</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">not_registered</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">static_peak_detector_sensitivity</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">generated</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">figures/static_peak_detector_sensitivity.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">static_peak_detector_summary</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">available</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">static_peak_detector_ppv</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">generated</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">figures/static_peak_detector_ppv.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">static_peak_detector_recording_metrics</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">not_registered</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">static_peak_detector_ppv</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">generated</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">figures/static_peak_detector_ppv.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">static_peak_detector_summary</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">available</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">static_peak_detector_interval_rmse</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">generated</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">figures/static_peak_detector_interval_rmse.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">static_peak_detector_recording_metrics</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">not_registered</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">static_peak_detector_interval_rmse</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">generated</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">figures/static_peak_detector_interval_rmse.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">static_peak_detector_summary</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">available</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">static_peak_detector_runtime</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">generated</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">figures/static_peak_detector_runtime.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">static_peak_detector_recording_metrics</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">not_registered</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">static_peak_detector_runtime</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">generated</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">figures/static_peak_detector_runtime.png</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">participating_cases</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">component_role</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">module_id</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">execution_state</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">input_data</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fixed_parameters</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">algorithm_kernel_description</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">reporter_profile_id</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">model_reporter_extension_id</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">algorithm_references</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">all</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dataset_adapter</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ptt_ppg_1_1_0_local</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">enabled</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"activities":["sit","walk","run"],"channels":{"IR":"pleth_2","RED":"pleth_1"},"dataset_id":"ptt_ppg_1_1_0_local","dataset_root":"physionet.org/files/pulse-transit-time-ppg/1.1.0","ecg_peak_annotation_column":"peaks","participants":22,"pipeline_fs_hz":400.0,"records":66,"source_fs_hz":500.0}</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"activities":["sit","walk","run"],"dataset_id":"ptt_ppg_1_1_0_local","distal_channels":{"IR":"pleth_2","RED":"pleth_1"},"ecg_peak_annotation_column":"peaks","participant_count":22,"record_count":66,"root":"physionet.org/files/pulse-transit-time-ppg/1.1.0","selected_activity":"sit","selected_record_count":22}</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Persisted dataset_adapter contract; detailed values remain in the component input and fixed-parameter fields.</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">audit_provenance_v1</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">audit_provenance_v1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Project component-role audit binding: dataset_adapter; no separate external literature source claimed</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
           <t xml:space="preserve">PTT sit static peak ablation</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">peak_detector</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">aboy_project_v1</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">executed</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"activities":["sit","walk","run"],"channels":["RED","IR"],"dataset_id":"ptt_ppg_1_1_0_local","dataset_root":"physionet.org/files/pulse-transit-time-ppg/1.1.0","ecg_peak_annotation_column":"peaks","input_view":null,"participants":22,"pipeline_fs_hz":400.0,"records":66,"scoring_windows_s":60.0,"selected_activity":"sit","source_fs_hz":500.0}</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"adaptive_bandpass_hz":"0.5 to min(8,max(1.5,3*(1+HRI)))","algorithm_id":"aboy_project_v1","bandpass_order":2,"block_s":10.0,"display_name":"aboy_project_v1","implementation":"ppg_frailty.peaks.aboy_project","initial_hri":0.0,"input_preprocessing":"shared repaired PPG then shared 0.2-8 Hz analysis filter","mad_limit":4.0,"mad_scale":1.4826,"prominence_fraction":0.25,"pulse_rate_bpm":[35.0,210.0],"registered_module_id":"aboy_project_v1","role":"current_project_reference"}</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Historical shared-preprocessing Aboy-family project detector.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">beat_detector_legacy_persisted_v1</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">audit_provenance_v1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Historical project adaptation; algorithm family: Aboy et al. (2005), DOI:10.1109/TBME.2005.855725</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PTT sit static peak ablation</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">peak_detector</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">msptdfast_v2_3_python_port</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">executed</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"activities":["sit","walk","run"],"channels":["RED","IR"],"dataset_id":"ptt_ppg_1_1_0_local","dataset_root":"physionet.org/files/pulse-transit-time-ppg/1.1.0","ecg_peak_annotation_column":"peaks","input_view":null,"participants":22,"pipeline_fs_hz":400.0,"records":66,"scoring_windows_s":60.0,"selected_activity":"sit","source_fs_hz":500.0}</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"algorithm_id":"msptdfast_v2_3_python_port","display_name":"msptdfast_v2_3_python_port","implementation":"ppg_frailty.quality.stage5_pre.detect_msptdfast_v2","parameters":{"minimum_heart_rate_bpm":30.0,"overlap_fraction":0.2,"target_downsample_hz":20.0,"window_s":6.0},"parity_status":"equation_level_port_not_bitwise_matlab_validated","registered_module_id":"msptdfast_v2_3_python_port","role":"paper_method_comparator"}</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Equation-level Python port of MSPTDfast (v.2); no bitwise MATLAB-parity claim.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">beat_detector_legacy_persisted_v1</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">audit_provenance_v1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Charlton et al. (2025), MSPTDfast (v.2), DOI:10.1088/1361-6579/adb89e</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PTT sit static peak ablation</t>
+        </is>
+      </c>
       <c r="B5" t="inlineStr">
         <is>
           <t xml:space="preserve">peak_validation</t>
@@ -649,7 +1352,22 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Persisted peak_validation contract; detailed values remain in the component input and fixed-parameter fields.</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">beat_detector_legacy_persisted_v1</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">audit_provenance_v1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Project component-role audit binding: peak_validation; no separate external literature source claimed</t>
         </is>
       </c>
     </row>
